--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488108_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488108_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9238</v>
+        <v>0.9053</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0574</v>
+        <v>0.9053</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1336</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6998</v>
+        <v>0.9053</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6305</v>
+        <v>0.3027</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.3303</v>
+        <v>0.6027</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2178</v>
+        <v>0.9053</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8165</v>
+        <v>0.3027</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5988</v>
+        <v>0.6027</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9176</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1861</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7315</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1619</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9627</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1992</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1408</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9053</v>
+        <v>0.6364</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9053</v>
+        <v>-0.5678</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.2042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9053</v>
+        <v>2.4192</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3027</v>
+        <v>2.6162</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6027</v>
+        <v>-0.197</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9053</v>
+        <v>2.1942</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3027</v>
+        <v>2.2668</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6027</v>
+        <v>-0.0726</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.3494</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.1244</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.3323</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.4707</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8975</v>
+        <v>0.2368</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8963</v>
+        <v>0.2861</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7938</v>
+        <v>-0.0493</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4192</v>
+        <v>-0.6998</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6162</v>
+        <v>1.6305</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.197</v>
+        <v>-2.3303</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1942</v>
+        <v>1.2178</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2668</v>
+        <v>1.8165</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0726</v>
+        <v>-0.5988</v>
       </c>
       <c r="M4" t="n">
-        <v>0.225</v>
+        <v>-1.9176</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3494</v>
+        <v>-0.1861</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1244</v>
+        <v>-1.7315</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.1982</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-1.9822</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-3.9645</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0641</v>
+        <v>1.4749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0038</v>
+        <v>1.1914</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0603</v>
+        <v>0.2835</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6036</v>
+        <v>-0.34</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8701</v>
+        <v>-0.1408</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4737</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5323</v>
+        <v>-0.1601</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.704</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3755</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7269</v>
@@ -844,13 +844,13 @@
         <v>0.5947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6071</v>
+        <v>-0.2349</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2386</v>
+        <v>-0.0348</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3686</v>
+        <v>-0.2001</v>
       </c>
       <c r="V5" t="n">
         <v>1.2071</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>A. MATEOS PENA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7237</v>
+        <v>-0.3019</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6462</v>
+        <v>-0.5583</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3699</v>
+        <v>0.2564</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.8925</v>
+        <v>-1.4665</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2854</v>
+        <v>-0.1427</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6071</v>
+        <v>-1.3238</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4251</v>
+        <v>-0.6708</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4251</v>
+        <v>0.1211</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.7919</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4674</v>
+        <v>-0.7957</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1398</v>
+        <v>-0.2638</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6071</v>
+        <v>-0.5319</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0499</v>
+        <v>-0.223</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5382</v>
+        <v>-0.1541</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5117</v>
+        <v>-0.0689</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MATEOS PENA</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7936</v>
+        <v>-0.8137</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9658</v>
+        <v>2.0161</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1722</v>
+        <v>-2.8298</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4665</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1427</v>
+        <v>-1.4543</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3238</v>
+        <v>0.4689</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6708</v>
+        <v>2.6919</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1211</v>
+        <v>1.0291</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7919</v>
+        <v>1.6628</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7957</v>
+        <v>-3.6773</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2638</v>
+        <v>-2.4833</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5319</v>
+        <v>-1.1939</v>
       </c>
       <c r="P7" t="n">
         <v>1.3876</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7147</v>
+        <v>-1.2159</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5616</v>
+        <v>-0.9423</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1531</v>
+        <v>-0.2735</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3002</v>
+        <v>-1.6053</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5857</v>
+        <v>-0.0669</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.886</v>
+        <v>-1.5384</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-2.8925</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4543</v>
+        <v>-1.2854</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4689</v>
+        <v>-1.6071</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6919</v>
+        <v>-1.4251</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0291</v>
+        <v>-1.4251</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6628</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.6773</v>
+        <v>-1.4674</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4833</v>
+        <v>0.1398</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1939</v>
+        <v>-1.6071</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7024</v>
+        <v>1.1683</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3727</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3297</v>
+        <v>0.3432</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0279</v>
+        <v>-1.6214</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.974</v>
+        <v>-1.7078</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0539</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0.244</v>
@@ -1156,13 +1156,13 @@
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.4689</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.624</v>
+        <v>-0.3578</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2515</v>
+        <v>-0.1111</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6036</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.517</v>
+        <v>-1.8153</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.164</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.353</v>
+        <v>-2.3249</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1782</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7411</v>
+        <v>-0.0394</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.2623</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1949</v>
+        <v>0.223</v>
       </c>
       <c r="V10" t="n">
         <v>1.8077</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0136</v>
+        <v>-2.133</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3313</v>
+        <v>-0.7595</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6824</v>
+        <v>-1.3735</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0548</v>
@@ -1312,13 +1312,13 @@
         <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1978</v>
+        <v>0.6828</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>0.4507</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.2321</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3468</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3707</v>
+        <v>-3.275</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2435</v>
+        <v>-2.26</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1273</v>
+        <v>-1.015</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7826</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1709</v>
+        <v>-0.0752</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3154</v>
+        <v>-0.332</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1445</v>
+        <v>0.2568</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2101</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4154</v>
+        <v>-6.4704</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2454</v>
+        <v>-5.1601</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1699</v>
+        <v>-1.3103</v>
       </c>
       <c r="G13" t="n">
         <v>-8.656499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6297</v>
+        <v>0.5746</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0769</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7065</v>
+        <v>0.5661</v>
       </c>
       <c r="V13" t="n">
         <v>1.6115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.796099999999999</v>
+        <v>-8.410399999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.4637</v>
+        <v>-3.9938</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.3324</v>
+        <v>-4.4166</v>
       </c>
       <c r="G14" t="n">
         <v>-4.7789</v>
@@ -1546,13 +1546,13 @@
         <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0876</v>
+        <v>-0.702</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2479</v>
+        <v>-0.7781</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1603</v>
+        <v>0.0761</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7403</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-25.7639</v>
+        <v>-24.828</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.9972</v>
+        <v>-12.0611</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.7669</v>
+        <v>-12.7668</v>
       </c>
       <c r="G15" t="n">
         <v>-26.6536</v>
@@ -1603,7 +1603,7 @@
         <v>1.2014</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.254800000000001</v>
+        <v>-6.254799999999999</v>
       </c>
       <c r="M15" t="n">
         <v>-21.6002</v>
@@ -1624,13 +1624,13 @@
         <v>14.8668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8085000000000007</v>
+        <v>1.7443</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9894000000000003</v>
+        <v>-0.0535000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7977</v>
+        <v>1.7979</v>
       </c>
       <c r="V15" t="n">
         <v>-2.8921</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9996</v>
+        <v>6.9567</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2678</v>
+        <v>5.7584</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7318</v>
+        <v>1.1983</v>
       </c>
       <c r="G16" t="n">
         <v>4.9244</v>
@@ -1702,13 +1702,13 @@
         <v>1.5858</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0485</v>
+        <v>1.0057</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3766</v>
+        <v>0.8431</v>
       </c>
       <c r="V16" t="n">
         <v>2.4142</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7339</v>
+        <v>5.1224</v>
       </c>
       <c r="E17" t="n">
         <v>4.0728</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6611</v>
+        <v>1.0496</v>
       </c>
       <c r="G17" t="n">
         <v>5.0478</v>
@@ -1780,13 +1780,13 @@
         <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3124</v>
+        <v>0.0761</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2568</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0556</v>
+        <v>0.3329</v>
       </c>
       <c r="V17" t="n">
         <v>-1.7855</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4261</v>
+        <v>3.7128</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7899</v>
+        <v>1.688</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6363</v>
+        <v>2.0248</v>
       </c>
       <c r="G18" t="n">
         <v>3.0353</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4996</v>
+        <v>-0.213</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0696</v>
+        <v>-0.1715</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.43</v>
+        <v>-0.0415</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1006</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.3173</v>
+        <v>3.5057</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5369</v>
+        <v>2.8743</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7803</v>
+        <v>0.6314</v>
       </c>
       <c r="G19" t="n">
-        <v>4.3364</v>
+        <v>2.7447</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5611</v>
+        <v>-0.6683</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7753</v>
+        <v>3.413</v>
       </c>
       <c r="J19" t="n">
-        <v>2.627</v>
+        <v>3.5173</v>
       </c>
       <c r="K19" t="n">
-        <v>1.944</v>
+        <v>0.2629</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6830000000000001</v>
+        <v>3.2544</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7094</v>
+        <v>-0.7725</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6171</v>
+        <v>-0.9312</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0923</v>
+        <v>0.1586</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
         <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6187</v>
+        <v>0.1</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3744</v>
+        <v>-0.1146</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9931</v>
+        <v>0.2146</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.845</v>
+        <v>0.4627</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>0.4627</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8278</v>
+        <v>3.1279</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3649</v>
+        <v>0.7407</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4629</v>
+        <v>2.3872</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7447</v>
+        <v>4.3364</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6683</v>
+        <v>2.5611</v>
       </c>
       <c r="I20" t="n">
-        <v>3.413</v>
+        <v>1.7753</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5173</v>
+        <v>2.627</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2629</v>
+        <v>1.944</v>
       </c>
       <c r="L20" t="n">
-        <v>3.2544</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7725</v>
+        <v>1.7094</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9312</v>
+        <v>0.6171</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1586</v>
+        <v>1.0923</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5778</v>
+        <v>0.4294</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.624</v>
+        <v>-0.1706</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0461</v>
+        <v>0.6</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4627</v>
+        <v>-0.845</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4627</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1115</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.544</v>
+        <v>3.0919</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9646</v>
+        <v>2.3721</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5794</v>
+        <v>0.7198</v>
       </c>
       <c r="G21" t="n">
         <v>2.0486</v>
@@ -2092,13 +2092,13 @@
         <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4718</v>
+        <v>0.0761</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4992</v>
+        <v>-0.0917</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0274</v>
+        <v>0.1678</v>
       </c>
       <c r="V21" t="n">
         <v>2.7512</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5226</v>
+        <v>2.217</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2901</v>
+        <v>-0.0155</v>
       </c>
       <c r="F22" t="n">
         <v>2.2325</v>
@@ -2170,10 +2170,10 @@
         <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>0.301</v>
+        <v>-0.0047</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3047</v>
+        <v>-0.0009</v>
       </c>
       <c r="U22" t="n">
         <v>-0.0038</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.752</v>
+        <v>1.9512</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8236</v>
+        <v>-1.6198</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5756</v>
+        <v>3.571</v>
       </c>
       <c r="G23" t="n">
         <v>1.4329</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5783</v>
+        <v>-0.3791</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7488</v>
+        <v>-0.545</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1705</v>
+        <v>0.1659</v>
       </c>
       <c r="V23" t="n">
         <v>0.6991000000000001</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>O. ZARACHO PAEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1307</v>
+        <v>-0.2258</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.1296</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2065</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9213</v>
+        <v>0.7195</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.4641</v>
+        <v>-1.3868</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4572</v>
+        <v>2.1063</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9349</v>
+        <v>0.9698</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3361</v>
+        <v>-0.3159</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5988</v>
+        <v>1.2857</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0136</v>
+        <v>-0.2503</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.128</v>
+        <v>-1.0709</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1415</v>
+        <v>0.8207</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5947</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4574</v>
+        <v>-0.3506</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8591</v>
+        <v>-0.1082</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4017</v>
+        <v>-0.2423</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>O. ZARACHO PAEZ</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,58 +2515,58 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6541</v>
+        <v>-0.6607</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3333</v>
+        <v>-0.8908</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3208</v>
+        <v>0.23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7195</v>
+        <v>-0.9213</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3868</v>
+        <v>-0.4641</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1063</v>
+        <v>-0.4572</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9698</v>
+        <v>-0.9349</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.3159</v>
+        <v>-0.3361</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2857</v>
+        <v>-0.5988</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2503</v>
+        <v>0.0136</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0709</v>
+        <v>-0.128</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8207</v>
+        <v>0.1415</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.5947</v>
+        <v>0.5947</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.779</v>
+        <v>-0.334</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.312</v>
+        <v>0.0441</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.467</v>
+        <v>-0.3782</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.044</v>
+        <v>-3.564</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.4955</v>
+        <v>-3.2918</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5485</v>
+        <v>-0.2723</v>
       </c>
       <c r="G28" t="n">
         <v>0.4702</v>
@@ -2638,13 +2638,13 @@
         <v>1.1893</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.0151</v>
+        <v>-0.5351</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7488</v>
+        <v>-0.545</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.2663</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="V28" t="n">
         <v>-1.7151</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>25.7639</v>
+        <v>26.4431</v>
       </c>
       <c r="E29" t="n">
         <v>12.7668</v>
       </c>
       <c r="F29" t="n">
-        <v>12.9971</v>
+        <v>13.6761</v>
       </c>
       <c r="G29" t="n">
         <v>26.6536</v>
@@ -2692,7 +2692,7 @@
         <v>21.6002</v>
       </c>
       <c r="K29" t="n">
-        <v>8.302999999999999</v>
+        <v>8.303000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>13.2976</v>
@@ -2704,7 +2704,7 @@
         <v>-1.2013</v>
       </c>
       <c r="O29" t="n">
-        <v>6.2547</v>
+        <v>6.254700000000001</v>
       </c>
       <c r="P29" t="n">
         <v>-2.9734</v>
@@ -2716,16 +2716,16 @@
         <v>11.8932</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.8083999999999997</v>
+        <v>-0.1291999999999998</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.7979</v>
+        <v>-1.7977</v>
       </c>
       <c r="U29" t="n">
-        <v>0.9892999999999998</v>
+        <v>1.6684</v>
       </c>
       <c r="V29" t="n">
-        <v>2.891899999999999</v>
+        <v>2.8919</v>
       </c>
       <c r="W29" t="n">
         <v>7.831200000000001</v>
